--- a/rules/CORE-000738/negative/01/data/unit-test-coreid-FB1106-negative-1.xlsx
+++ b/rules/CORE-000738/negative/01/data/unit-test-coreid-FB1106-negative-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000738\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372A4DF6-236C-4360-867D-55D39229A1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69B9624-8A82-4E50-9B14-1B2083073DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -361,7 +361,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -385,10 +385,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -815,24 +812,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D04F57-0AF2-4977-8A17-3F884A80F209}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="7" t="s">
         <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -1073,13 +1073,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="7">
         <v>20</v>
       </c>
       <c r="H6" s="7"/>
@@ -1239,13 +1239,13 @@
       <c r="D12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>68</v>
       </c>
       <c r="H12" s="7"/>
@@ -1305,16 +1305,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d36826f407302d9fd93d8089214679b0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="257daeb82d9c284d9d656fb5e9ad601e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1554,6 +1544,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DFFF2B-AFAE-466C-A5DC-966DF9457202}">
   <ds:schemaRefs>
@@ -1563,17 +1563,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB30A1-25F5-4D6B-AA9C-850DE868D543}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8759A8-0041-4F67-B14B-FEE1B72EE774}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1591,4 +1580,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1BB30A1-25F5-4D6B-AA9C-850DE868D543}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>